--- a/qlb_colony_spreadsheet.xlsx
+++ b/qlb_colony_spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sheinasim/Bioinformatic_software/sheinasim.github.io/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usdagcc-my.sharepoint.com/personal/sheina_sim_usda_gov/Documents/Projects/Dashboard/sheinasim.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E79CA08-09BD-E04C-8D25-9DEEB81A32E7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3E79CA08-09BD-E04C-8D25-9DEEB81A32E7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{8910B4DB-A138-D34C-99A7-2FA921AB4154}"/>
   <bookViews>
-    <workbookView xWindow="-29000" yWindow="4300" windowWidth="29020" windowHeight="9940" xr2:uid="{B6248D05-47C7-5D4A-B216-529F4D1EBA26}"/>
+    <workbookView xWindow="-32720" yWindow="60" windowWidth="29020" windowHeight="9940" xr2:uid="{B6248D05-47C7-5D4A-B216-529F4D1EBA26}"/>
   </bookViews>
   <sheets>
     <sheet name="lifestages" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
     <t>Adult male</t>
   </si>
   <si>
-    <t>2021March12</t>
+    <t>2021.03.12</t>
   </si>
 </sst>
 </file>

--- a/qlb_colony_spreadsheet.xlsx
+++ b/qlb_colony_spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10323"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usdagcc-my.sharepoint.com/personal/sheina_sim_usda_gov/Documents/Projects/Dashboard/sheinasim.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3E79CA08-09BD-E04C-8D25-9DEEB81A32E7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{8910B4DB-A138-D34C-99A7-2FA921AB4154}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{3E79CA08-09BD-E04C-8D25-9DEEB81A32E7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{E2B2392A-2590-864F-8D36-8BC98991DF94}"/>
   <bookViews>
     <workbookView xWindow="-32720" yWindow="60" windowWidth="29020" windowHeight="9940" xr2:uid="{B6248D05-47C7-5D4A-B216-529F4D1EBA26}"/>
   </bookViews>
@@ -34,17 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Larvae</t>
-  </si>
-  <si>
-    <t>Pupae</t>
-  </si>
-  <si>
     <t>Adult mating</t>
   </si>
   <si>
@@ -55,6 +49,15 @@
   </si>
   <si>
     <t>2021.03.12</t>
+  </si>
+  <si>
+    <t>2021.03.26</t>
+  </si>
+  <si>
+    <t>Larva</t>
+  </si>
+  <si>
+    <t>Pupa</t>
   </si>
 </sst>
 </file>
@@ -406,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9733DE3B-5FDD-0C4D-B4BD-B6BB1E04A6F3}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -418,24 +421,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>8</v>
@@ -450,6 +453,26 @@
         <v>2</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>53</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
         <v>0</v>
       </c>
     </row>
